--- a/input_tool/edu_indicator_labelling.xlsx
+++ b/input_tool/edu_indicator_labelling.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted-my.sharepoint.com/personal/martina_vit_impact-initiatives_org/Documents/MSNAEdu/EduAnalysisTool/input_tool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yann SAY\Desktop\git\EduAnalysisTool\input_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{D3462D9F-D80F-4473-B948-1519E83722D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{763A8EFD-BBFF-4052-9FC1-CBAEDCDC57B4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F4E542-07A5-4989-BF60-2FB4839FDC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update_survey" sheetId="6" r:id="rId1"/>
     <sheet name="update_choices" sheetId="7" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">update_choices!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">update_choices!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">update_survey!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -289,9 +289,6 @@
     <t>no_efford</t>
   </si>
   <si>
-    <t>Cannot afford the direct costs of education (e.g. tuition, supplies, transportation)</t>
-  </si>
-  <si>
     <t>lack_intrest</t>
   </si>
   <si>
@@ -349,9 +346,6 @@
     <t>child_work</t>
   </si>
   <si>
-    <t xml:space="preserve">Child needs to work at home or on the household's own farm (i.e. is not earning an income for these activities, but may allow other family members to earn an income) </t>
-  </si>
-  <si>
     <t>child_income</t>
   </si>
   <si>
@@ -391,9 +385,6 @@
     <t>displacement_issu</t>
   </si>
   <si>
-    <t>Unable to enroll in school due to recent displacement/return (displacement since after the start of the school year)</t>
-  </si>
-  <si>
     <t>discrimination</t>
   </si>
   <si>
@@ -430,9 +421,6 @@
     <t xml:space="preserve">Risques de protection pendant le trajet vers l'école </t>
   </si>
   <si>
-    <t>L'enfant doit travailler à la maison ou dans la ferme du ménage (c'est-à-dire qu'il ne gagne pas de revenu pour ces activités, mais peut permettre à d'autres membres de la famille de gagner un revenu)</t>
-  </si>
-  <si>
     <t>L'enfant participe à des activités génératrices de revenus en dehors du foyer</t>
   </si>
   <si>
@@ -451,18 +439,12 @@
     <t>Impossibilité de s'inscrire à l'école en raison d'un manque de documents</t>
   </si>
   <si>
-    <t>Impossibilité de s'inscrire à l'école en raison d'un déplacement/retour récent (déplacement après le début de l'année scolaire)</t>
-  </si>
-  <si>
     <t>Discrimination ou stigmatisation de l'enfant pour quelque raison que ce soit</t>
   </si>
   <si>
     <t xml:space="preserve">L'enfant est déjà diplômé de l'enseignement secondaire. </t>
   </si>
   <si>
-    <t>Impossibilité de payer les coûts directs de l'éducation (par exemple, les frais de scolarité, les fournitures, le transport)</t>
-  </si>
-  <si>
     <t>% of school-aged children attending primary school who are at least 2 years above the intended age for their grade</t>
   </si>
   <si>
@@ -482,6 +464,24 @@
   </si>
   <si>
     <t>% de ménages avec enfants de 5 à 18 ans par moyens d'améliorer l'éducation</t>
+  </si>
+  <si>
+    <t>Cannot afford the direct costs of education</t>
+  </si>
+  <si>
+    <t>Child needs to work at home or on the household's own farm</t>
+  </si>
+  <si>
+    <t>Unable to enroll in school due to recent displacement/return</t>
+  </si>
+  <si>
+    <t>Impossibilité de s'inscrire à l'école en raison d'un déplacement/retour récent</t>
+  </si>
+  <si>
+    <t>Impossibilité de payer les coûts directs de l'éducation</t>
+  </si>
+  <si>
+    <t>L'enfant doit travailler à la maison ou dans la ferme du ménage</t>
   </si>
 </sst>
 </file>
@@ -898,17 +898,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.75" x14ac:dyDescent="0.95"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.69921875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="41.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="94.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="52.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="41.69921875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="94.8984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="52.19921875" style="3" customWidth="1"/>
     <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.95">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -925,7 +925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -942,7 +942,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -959,7 +959,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -976,7 +976,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -993,7 +993,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -1021,13 +1021,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.95">
+    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -1242,13 +1242,13 @@
         <v>31</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>1</v>
       </c>
@@ -1259,13 +1259,13 @@
         <v>32</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="26.5" x14ac:dyDescent="0.95">
+    <row r="23" spans="1:5" ht="26.4" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
@@ -1313,10 +1313,10 @@
         <v>33</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.95">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
@@ -1324,24 +1324,24 @@
         <v>6</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.95">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.95">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
@@ -1359,17 +1359,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.75" x14ac:dyDescent="0.95"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="36.125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="36.09765625" style="5" customWidth="1"/>
     <col min="2" max="2" width="21.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="26.875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="30.375" style="5" customWidth="1"/>
-    <col min="5" max="8" width="12.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="54.3984375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="30.3984375" style="5" customWidth="1"/>
+    <col min="5" max="8" width="12.69921875" style="5" customWidth="1"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.95">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.95">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>76</v>
       </c>
@@ -1406,10 +1406,10 @@
         <v>79</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.95">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>76</v>
       </c>
@@ -1417,279 +1417,279 @@
         <v>80</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A4" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.95">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="6" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="6" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A8" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="6" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="6" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="6" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="6" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="6" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="6" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="6" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A15" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="6" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.95">
-      <c r="A16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="6" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.95">
-      <c r="A17" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="6" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.95">
-      <c r="A18" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.95">
-      <c r="A19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.95">
-      <c r="A20" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.95">
-      <c r="A21" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.95">
-      <c r="A22" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.95">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
         <v>76</v>
       </c>
@@ -1703,16 +1703,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.95">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.95">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
+  <autoFilter ref="A1:H23" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/input_tool/edu_indicator_labelling.xlsx
+++ b/input_tool/edu_indicator_labelling.xlsx
@@ -8,32 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\albertoramirez\Projects\EduAnalysisTool-v2-worktrees\main-config-validation\input_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60E814B-3F92-4257-AA15-BA7E71F58FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAF8901-9C36-4FC6-B9A1-00D39C4DEF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="-15870" windowWidth="25440" windowHeight="15990" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="834" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update_survey" sheetId="6" r:id="rId1"/>
     <sheet name="original" sheetId="22" r:id="rId2"/>
-    <sheet name="bfa" sheetId="21" r:id="rId3"/>
-    <sheet name="lbn" sheetId="20" r:id="rId4"/>
-    <sheet name="hti" sheetId="19" r:id="rId5"/>
-    <sheet name="eth" sheetId="18" r:id="rId6"/>
-    <sheet name="drc" sheetId="17" r:id="rId7"/>
-    <sheet name="ssd" sheetId="16" r:id="rId8"/>
-    <sheet name="som" sheetId="15" r:id="rId9"/>
-    <sheet name="mmr" sheetId="14" r:id="rId10"/>
-    <sheet name="mali" sheetId="13" r:id="rId11"/>
-    <sheet name="ken" sheetId="12" r:id="rId12"/>
-    <sheet name="moz" sheetId="11" r:id="rId13"/>
-    <sheet name="update_choices" sheetId="7" r:id="rId14"/>
-    <sheet name="car" sheetId="8" r:id="rId15"/>
-    <sheet name="afg" sheetId="9" r:id="rId16"/>
-    <sheet name="sdn" sheetId="10" r:id="rId17"/>
+    <sheet name="update_choices" sheetId="7" r:id="rId3"/>
+    <sheet name="OPT" sheetId="23" r:id="rId4"/>
+    <sheet name="BFA" sheetId="21" r:id="rId5"/>
+    <sheet name="LBN" sheetId="20" r:id="rId6"/>
+    <sheet name="HTI" sheetId="19" r:id="rId7"/>
+    <sheet name="ETH" sheetId="18" r:id="rId8"/>
+    <sheet name="DRC" sheetId="17" r:id="rId9"/>
+    <sheet name="SSD" sheetId="16" r:id="rId10"/>
+    <sheet name="SOM" sheetId="15" r:id="rId11"/>
+    <sheet name="MMR" sheetId="14" r:id="rId12"/>
+    <sheet name="MLI" sheetId="13" r:id="rId13"/>
+    <sheet name="KEN" sheetId="12" r:id="rId14"/>
+    <sheet name="MOZ" sheetId="11" r:id="rId15"/>
+    <sheet name="CAR" sheetId="8" r:id="rId16"/>
+    <sheet name="AFG" sheetId="9" r:id="rId17"/>
+    <sheet name="SDN" sheetId="10" r:id="rId18"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">OPT!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">original!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">update_choices!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">update_choices!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">update_survey!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="237">
   <si>
     <t>theme</t>
   </si>
@@ -1723,7 +1725,7 @@
       </c>
       <c r="F24" s="26"/>
     </row>
-    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
         <v>1</v>
       </c>
@@ -1740,7 +1742,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
         <v>1</v>
       </c>
@@ -1980,11 +1982,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBB2A30-1E77-42F1-964E-A72E9BDDBED9}">
-  <dimension ref="A1:F39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C98E618-344A-487D-B00E-EFB2C24E3770}">
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="53.5" style="7"/>
+    <col min="1" max="1" width="19.19921875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="16.3984375" style="7" customWidth="1"/>
     <col min="3" max="5" width="53.5" style="15"/>
     <col min="6" max="16384" width="53.5" style="7"/>
   </cols>
@@ -2206,7 +2209,7 @@
         <v>169</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>49</v>
@@ -2380,7 +2383,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>197</v>
@@ -2643,6 +2646,23 @@
       </c>
       <c r="D39" s="15" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A40" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2661,7 +2681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FDAFB7B-CACC-4A95-AEE0-FBF416C1C9E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA04313-1E16-4C5B-AB02-8927EAB717AE}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
@@ -2887,7 +2907,7 @@
         <v>169</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>49</v>
@@ -2907,7 +2927,7 @@
         <v>43</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>202</v>
+        <v>47</v>
       </c>
       <c r="F14" s="26"/>
     </row>
@@ -2922,10 +2942,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>203</v>
+        <v>230</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>49</v>
       </c>
       <c r="F15" s="28"/>
     </row>
@@ -2940,10 +2960,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>233</v>
+        <v>225</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>48</v>
       </c>
       <c r="F16" s="28"/>
     </row>
@@ -3046,7 +3066,7 @@
         <v>106</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F22" s="26"/>
     </row>
@@ -3061,10 +3081,10 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F23" s="26"/>
     </row>
@@ -3079,10 +3099,10 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F24" s="26"/>
     </row>
@@ -3342,7 +3362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C9AFB8-F0F3-4AAA-AA27-0292EA78AA26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBB2A30-1E77-42F1-964E-A72E9BDDBED9}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3603,7 +3623,7 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>49</v>
@@ -3621,7 +3641,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>48</v>
@@ -3742,7 +3762,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>197</v>
@@ -3760,7 +3780,7 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>198</v>
@@ -4023,7 +4043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3426F2-D478-46D5-B931-E2053F6BF542}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FDAFB7B-CACC-4A95-AEE0-FBF416C1C9E5}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4269,7 +4289,7 @@
         <v>43</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>47</v>
+        <v>202</v>
       </c>
       <c r="F14" s="26"/>
     </row>
@@ -4284,10 +4304,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>49</v>
+        <v>199</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>203</v>
       </c>
       <c r="F15" s="28"/>
     </row>
@@ -4302,10 +4322,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>48</v>
+        <v>232</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>233</v>
       </c>
       <c r="F16" s="28"/>
     </row>
@@ -4408,7 +4428,7 @@
         <v>106</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F22" s="26"/>
     </row>
@@ -4423,10 +4443,10 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F23" s="26"/>
     </row>
@@ -4441,10 +4461,10 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="F24" s="26"/>
     </row>
@@ -4704,472 +4724,1368 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C9AFB8-F0F3-4AAA-AA27-0292EA78AA26}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="36.09765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="54.3984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.3984375" style="1" customWidth="1"/>
-    <col min="5" max="8" width="12.69921875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="53.5" style="7"/>
+    <col min="3" max="5" width="53.5" style="15"/>
+    <col min="6" max="16384" width="53.5" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A29" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>140</v>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="26"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="26"/>
+    </row>
+    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="26"/>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F23" s="26"/>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="26"/>
+    </row>
+    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H19" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <mergeCells count="8">
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E22:F22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3426F2-D478-46D5-B931-E2053F6BF542}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="53.5" style="7"/>
+    <col min="3" max="5" width="53.5" style="15"/>
+    <col min="6" max="16384" width="53.5" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="26"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="26"/>
+    </row>
+    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="26"/>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F23" s="26"/>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="26"/>
+    </row>
+    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E22:F22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93BDC91-E487-4F88-AEAB-B2FA5E4CA8B4}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -5851,7 +6767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04631CBF-6FD9-45D1-9C42-22D5C9F097A4}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -6533,7 +7449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E3B9F7-D347-4317-AB67-0217058F4008}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -7649,7 +8565,7 @@
       </c>
       <c r="F24" s="26"/>
     </row>
-    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
         <v>1</v>
       </c>
@@ -7666,7 +8582,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
         <v>1</v>
       </c>
@@ -7906,6 +8822,1157 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="36.09765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.3984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.3984375" style="1" customWidth="1"/>
+    <col min="5" max="8" width="12.69921875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H19" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37EE543-B5CB-4185-B91B-2A9A8CC3DA4C}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.5" style="7" customWidth="1"/>
+    <col min="2" max="2" width="26.59765625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="53.5" style="15"/>
+    <col min="4" max="4" width="106.5" style="15" customWidth="1"/>
+    <col min="5" max="5" width="53.5" style="15"/>
+    <col min="6" max="16384" width="53.5" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="26"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="26"/>
+    </row>
+    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="26"/>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F23" s="26"/>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="26"/>
+    </row>
+    <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E22:F22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78ED0E70-DB3B-451B-8866-F48A2CB32CE9}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -8587,7 +10654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B023821-20D2-4192-846D-05966B68C2F4}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -9269,7 +11336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E598F01-CD75-4BC5-AD14-CB9738585B67}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -9951,7 +12018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664A1F51-322B-4DAC-988D-ED5F1BCA03D1}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -10638,7 +12705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1430A0F1-2F5D-43E5-9E49-8E679EDD81F4}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -11323,1384 +13390,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C98E618-344A-487D-B00E-EFB2C24E3770}">
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="19.19921875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="16.3984375" style="7" customWidth="1"/>
-    <col min="3" max="5" width="53.5" style="15"/>
-    <col min="6" max="16384" width="53.5" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="26"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="26"/>
-    </row>
-    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="26"/>
-    </row>
-    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
-    </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
-    </row>
-    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
-    </row>
-    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E22:F22"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA04313-1E16-4C5B-AB02-8927EAB717AE}">
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="2" width="53.5" style="7"/>
-    <col min="3" max="5" width="53.5" style="15"/>
-    <col min="6" max="16384" width="53.5" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="26"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="26"/>
-    </row>
-    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="26"/>
-    </row>
-    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
-    </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
-    </row>
-    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
-    </row>
-    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E22:F22"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/input_tool/edu_indicator_labelling.xlsx
+++ b/input_tool/edu_indicator_labelling.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\albertoramirez\Projects\EduAnalysisTool-v2-worktrees\main-config-validation\input_tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\albertoramirez\Projects\EduAnalysisTool-v2-worktrees\strata-lvl-metadata\input_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAF8901-9C36-4FC6-B9A1-00D39C4DEF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865E928E-0D7A-4E5C-849C-67014FEBC9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="834" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update_survey" sheetId="6" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="240">
   <si>
     <t>theme</t>
   </si>
@@ -622,9 +622,6 @@
     <t>% d'enfants avec 2 ans de plus que l'âge prévu : enseignement Secondaire</t>
   </si>
   <si>
-    <t>% of school-aged children of intermediate school level age currently attending primary second cycle or higher</t>
-  </si>
-  <si>
     <t>% of school-aged children attending primary second cycle who are at least 2 years above the intended age for their grade</t>
   </si>
   <si>
@@ -773,13 +770,25 @@
   </si>
   <si>
     <t xml:space="preserve">Le programme scolaire et/ou les certificats délivrés par l'école ne sont pas perçus comme utiles pour le ménage. </t>
+  </si>
+  <si>
+    <t>% of school-aged children of primary school age currently attending primary education or higher</t>
+  </si>
+  <si>
+    <t>% of school-aged children of lower secondary school age currently attending lower secondary education level or higher</t>
+  </si>
+  <si>
+    <t>% of school-aged children of upper secondary secondary school age currently attending secondary school or higher</t>
+  </si>
+  <si>
+    <t>% of school-aged children attending lower secondary school age who are at least 2 years above the intended age for their grade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -881,8 +890,25 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF58585A"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF58585A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -919,8 +945,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9BBBB"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEAE2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF49999"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDCBCD"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -941,6 +991,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -951,7 +1049,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1022,11 +1120,51 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="6" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="5" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="6" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="20% - Accent6" xfId="6" builtinId="50"/>
@@ -1310,10 +1448,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="31" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="15" t="s">
@@ -1325,46 +1463,49 @@
       <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
-      </c>
+      <c r="F2" s="31"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="F3" s="31"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -1373,15 +1514,16 @@
       <c r="D4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="32" t="s">
         <v>44</v>
       </c>
+      <c r="F4" s="31"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -1393,12 +1535,13 @@
       <c r="E5" s="15" t="s">
         <v>176</v>
       </c>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -1410,12 +1553,13 @@
       <c r="E6" s="15" t="s">
         <v>45</v>
       </c>
+      <c r="F6" s="31"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
@@ -1427,12 +1571,13 @@
       <c r="E7" s="15" t="s">
         <v>126</v>
       </c>
+      <c r="F7" s="31"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -1444,12 +1589,13 @@
       <c r="E8" s="15" t="s">
         <v>160</v>
       </c>
+      <c r="F8" s="31"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -1461,309 +1607,319 @@
       <c r="E9" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="F9" s="31"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="43"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="44"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="A12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="34" t="s">
         <v>47</v>
       </c>
+      <c r="F12" s="33"/>
     </row>
     <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="17" t="s">
+      <c r="A13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="34" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="18" t="s">
+      <c r="F13" s="33"/>
+    </row>
+    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="47"/>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="48"/>
+    </row>
+    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="35"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A17" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E17" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
-    </row>
-    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="27" t="s">
+      <c r="F17" s="37"/>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A18" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="18" t="s">
+      <c r="F18" s="37"/>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A19" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E19" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="19" t="s">
+      <c r="F19" s="37"/>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A20" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="38" t="s">
         <v>50</v>
       </c>
+      <c r="F20" s="37"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="A21" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>161</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="20" t="s">
+      <c r="F21" s="31"/>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
-    </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="20" t="s">
+      <c r="E22" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" s="51"/>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
-    </row>
-    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="20" t="s">
+      <c r="D23" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="51"/>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+      <c r="D24" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="F24" s="52"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="A25" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
       </c>
+      <c r="F25" s="31"/>
     </row>
     <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="A26" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="31" t="s">
         <v>127</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
-      </c>
+      <c r="F26" s="31"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="7" t="s">
+      <c r="A27" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="15" t="s">
@@ -1775,12 +1931,13 @@
       <c r="E27" s="22" t="s">
         <v>111</v>
       </c>
+      <c r="F27" s="31"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="7" t="s">
+      <c r="A28" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="15" t="s">
@@ -1792,114 +1949,121 @@
       <c r="E28" s="15" t="s">
         <v>110</v>
       </c>
+      <c r="F28" s="31"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
+      <c r="A29" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
       </c>
+      <c r="F29" s="31"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="7" t="s">
+      <c r="A30" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
       </c>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="7" t="s">
+      <c r="A31" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="15" t="s">
         <v>150</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>154</v>
       </c>
+      <c r="F31" s="31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="7" t="s">
+      <c r="A32" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="15" t="s">
         <v>151</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="F32" s="31"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="15" t="s">
         <v>152</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
+      <c r="F33" s="31"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="15" t="s">
         <v>153</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="7" t="s">
+      <c r="F34" s="31"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="15" t="s">
@@ -1908,12 +2072,13 @@
       <c r="D35" s="15" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
+      <c r="F35" s="31"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="15" t="s">
@@ -1922,12 +2087,13 @@
       <c r="D36" s="15" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="7" t="s">
+      <c r="F36" s="31"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="15" t="s">
@@ -1936,12 +2102,13 @@
       <c r="D37" s="15" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
+      <c r="F37" s="31"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="15" t="s">
@@ -1950,12 +2117,13 @@
       <c r="D38" s="15" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
+      <c r="F38" s="31"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="15" t="s">
@@ -1964,9 +2132,10 @@
       <c r="D39" s="15" t="s">
         <v>175</v>
       </c>
+      <c r="F39" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E24:F24"/>
@@ -1974,7 +2143,6 @@
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2020,10 +2188,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -2037,10 +2205,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2158,10 +2326,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -2176,10 +2344,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -2209,7 +2377,7 @@
         <v>169</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>49</v>
@@ -2228,10 +2396,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -2244,9 +2412,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -2262,9 +2430,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -2314,7 +2482,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -2331,7 +2499,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -2348,10 +2516,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -2367,10 +2535,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -2383,12 +2551,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>209</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -2401,12 +2569,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>207</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -2419,7 +2587,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -2436,10 +2604,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -2487,7 +2655,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -2504,7 +2672,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -2653,16 +2821,16 @@
         <v>1</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D40" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E40" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2718,10 +2886,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -2735,10 +2903,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -2856,10 +3024,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -2874,10 +3042,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -2907,7 +3075,7 @@
         <v>169</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>49</v>
@@ -2926,10 +3094,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -2942,9 +3110,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -2960,9 +3128,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -3012,7 +3180,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -3029,7 +3197,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -3046,10 +3214,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -3065,10 +3233,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -3081,12 +3249,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>209</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -3099,12 +3267,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>207</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -3117,7 +3285,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -3134,10 +3302,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -3185,7 +3353,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -3202,7 +3370,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -3399,10 +3567,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -3416,10 +3584,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -3537,10 +3705,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -3555,10 +3723,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -3607,10 +3775,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -3623,9 +3791,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -3641,9 +3809,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -3693,7 +3861,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -3710,7 +3878,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -3727,10 +3895,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -3746,10 +3914,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -3762,12 +3930,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>206</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -3780,12 +3948,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>207</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -3798,7 +3966,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -3815,10 +3983,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -3866,7 +4034,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -3883,7 +4051,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -4080,10 +4248,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -4097,10 +4265,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -4218,10 +4386,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -4236,10 +4404,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -4288,10 +4456,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="F14" s="26"/>
+      <c r="E14" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -4304,10 +4472,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F15" s="28"/>
     </row>
@@ -4322,10 +4490,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="E16" s="30" t="s">
         <v>232</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>233</v>
       </c>
       <c r="F16" s="28"/>
     </row>
@@ -4374,7 +4542,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -4391,7 +4559,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -4408,10 +4576,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -4427,10 +4595,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -4443,12 +4611,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>199</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -4461,12 +4629,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>200</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -4479,7 +4647,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -4496,10 +4664,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -4547,7 +4715,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -4564,7 +4732,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -4761,10 +4929,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -4778,10 +4946,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -4899,10 +5067,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -4917,10 +5085,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -4969,10 +5137,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -4985,9 +5153,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -5003,9 +5171,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -5055,7 +5223,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -5072,7 +5240,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -5089,10 +5257,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -5108,10 +5276,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -5124,12 +5292,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>199</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -5142,12 +5310,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>200</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -5160,7 +5328,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -5177,10 +5345,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -5228,7 +5396,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -5245,7 +5413,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -5442,10 +5610,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -5459,10 +5627,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -5580,10 +5748,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -5598,10 +5766,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -5650,10 +5818,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -5666,9 +5834,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -5684,9 +5852,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -5736,7 +5904,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -5753,7 +5921,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -5770,10 +5938,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -5789,10 +5957,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -5805,12 +5973,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>188</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -5823,12 +5991,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>189</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -5841,7 +6009,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -5858,10 +6026,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -5909,7 +6077,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -5926,7 +6094,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -6126,10 +6294,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -6143,10 +6311,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -6264,10 +6432,10 @@
       <c r="D10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -6282,10 +6450,10 @@
       <c r="D11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
@@ -6334,10 +6502,10 @@
       <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -6352,10 +6520,10 @@
       <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F15" s="26"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
@@ -6368,7 +6536,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>48</v>
@@ -6419,7 +6587,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>48</v>
@@ -6436,7 +6604,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>50</v>
@@ -6453,10 +6621,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -6472,10 +6640,10 @@
       <c r="D22" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="26"/>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -6490,10 +6658,10 @@
       <c r="D23" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="F23" s="26"/>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
@@ -6506,12 +6674,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E24" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="26"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -6524,7 +6692,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>143</v>
@@ -6541,10 +6709,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -6592,7 +6760,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>158</v>
@@ -6609,7 +6777,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>159</v>
@@ -6781,10 +6949,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="31" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="15" t="s">
@@ -6796,46 +6964,49 @@
       <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
-      </c>
+      <c r="F2" s="31"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="F3" s="31"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -6844,15 +7015,16 @@
       <c r="D4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="32" t="s">
         <v>44</v>
       </c>
+      <c r="F4" s="31"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -6864,12 +7036,13 @@
       <c r="E5" s="15" t="s">
         <v>176</v>
       </c>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -6881,12 +7054,13 @@
       <c r="E6" s="15" t="s">
         <v>45</v>
       </c>
+      <c r="F6" s="31"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
@@ -6898,12 +7072,13 @@
       <c r="E7" s="15" t="s">
         <v>126</v>
       </c>
+      <c r="F7" s="31"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -6915,12 +7090,13 @@
       <c r="E8" s="15" t="s">
         <v>160</v>
       </c>
+      <c r="F8" s="31"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -6932,12 +7108,13 @@
       <c r="E9" s="15" t="s">
         <v>46</v>
       </c>
+      <c r="F9" s="31"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="15" t="s">
@@ -6946,16 +7123,16 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="43"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -6964,276 +7141,286 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="44"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="A12" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="34" t="s">
         <v>47</v>
       </c>
+      <c r="F12" s="33"/>
     </row>
     <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="17" t="s">
+      <c r="A13" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="34" t="s">
         <v>49</v>
       </c>
+      <c r="F13" s="33"/>
     </row>
     <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A14" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="18" t="s">
+      <c r="A14" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="47"/>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="48"/>
+    </row>
+    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="35"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A17" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="F14" s="28"/>
-    </row>
-    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="18" t="s">
+      <c r="E17" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="37"/>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A18" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="37"/>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A19" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="37"/>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A20" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="38" t="s">
         <v>50</v>
       </c>
+      <c r="F20" s="37"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="A21" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>161</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
-      </c>
+      <c r="F21" s="31"/>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="20" t="s">
+      <c r="A22" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="29"/>
+      <c r="F22" s="51"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A23" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="20" t="s">
+      <c r="A23" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="29" t="s">
+      <c r="D23" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="F23" s="29"/>
+      <c r="F23" s="51"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A24" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="20" t="s">
+      <c r="A24" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="E24" s="29" t="s">
+      <c r="D24" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="49" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="29"/>
+      <c r="F24" s="52"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="A25" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
       </c>
+      <c r="F25" s="31"/>
     </row>
     <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="A26" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="31" t="s">
         <v>127</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
-      </c>
+      <c r="F26" s="31"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="7" t="s">
+      <c r="A27" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="15" t="s">
@@ -7245,12 +7432,13 @@
       <c r="E27" s="22" t="s">
         <v>111</v>
       </c>
+      <c r="F27" s="31"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="7" t="s">
+      <c r="A28" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="15" t="s">
@@ -7262,114 +7450,121 @@
       <c r="E28" s="15" t="s">
         <v>110</v>
       </c>
+      <c r="F28" s="31"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
+      <c r="A29" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
       </c>
+      <c r="F29" s="31"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="7" t="s">
+      <c r="A30" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
       </c>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="7" t="s">
+      <c r="A31" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="15" t="s">
         <v>150</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>154</v>
       </c>
+      <c r="F31" s="31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="7" t="s">
+      <c r="A32" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="15" t="s">
         <v>151</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="7" t="s">
+      <c r="F32" s="31"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="15" t="s">
         <v>152</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
+      <c r="F33" s="31"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="15" t="s">
         <v>153</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="7" t="s">
+      <c r="F34" s="31"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="15" t="s">
@@ -7378,12 +7573,13 @@
       <c r="D35" s="15" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
+      <c r="F35" s="31"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="15" t="s">
@@ -7392,12 +7588,13 @@
       <c r="D36" s="15" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="7" t="s">
+      <c r="F36" s="31"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="15" t="s">
@@ -7406,12 +7603,13 @@
       <c r="D37" s="15" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
+      <c r="F37" s="31"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="15" t="s">
@@ -7420,12 +7618,13 @@
       <c r="D38" s="15" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
+      <c r="F38" s="31"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="15" t="s">
@@ -7434,6 +7633,7 @@
       <c r="D39" s="15" t="s">
         <v>175</v>
       </c>
+      <c r="F39" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7490,10 +7690,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -7507,10 +7707,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -7628,10 +7828,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -7646,10 +7846,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -7714,10 +7914,10 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>190</v>
       </c>
       <c r="F15" s="28"/>
     </row>
@@ -7732,10 +7932,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>192</v>
+        <v>233</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>191</v>
       </c>
       <c r="F16" s="28"/>
     </row>
@@ -7784,7 +7984,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -7801,7 +8001,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -7818,10 +8018,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.4">
@@ -7838,10 +8038,10 @@
         <v>106</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.4">
@@ -7855,13 +8055,13 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.4">
@@ -7875,13 +8075,13 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
@@ -7895,7 +8095,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -7912,10 +8112,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -7963,7 +8163,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -7980,7 +8180,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -8177,10 +8377,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -8194,10 +8394,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -8315,10 +8515,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -8333,10 +8533,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -8385,10 +8585,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -8401,9 +8601,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -8419,9 +8619,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -8471,7 +8671,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -8488,7 +8688,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -8505,10 +8705,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -8524,10 +8724,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -8540,12 +8740,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>212</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -8558,12 +8758,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>207</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -8576,7 +8776,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -8593,10 +8793,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -8644,7 +8844,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -8661,7 +8861,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -8952,10 +9152,10 @@
         <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -9328,10 +9528,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -9345,10 +9545,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -9466,10 +9666,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -9484,10 +9684,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -9536,10 +9736,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -9552,9 +9752,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -9570,9 +9770,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -9622,7 +9822,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -9639,7 +9839,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -9656,10 +9856,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -9675,10 +9875,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -9691,12 +9891,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>213</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -9709,12 +9909,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>209</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -9727,7 +9927,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -9744,10 +9944,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -9795,7 +9995,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -9812,7 +10012,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -10013,10 +10213,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -10030,10 +10230,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -10151,10 +10351,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -10169,10 +10369,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -10255,7 +10455,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>48</v>
@@ -10306,7 +10506,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -10323,7 +10523,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -10340,10 +10540,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
@@ -10359,10 +10559,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="29"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
@@ -10375,12 +10575,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="F23" s="29"/>
+      <c r="F23" s="26"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
@@ -10393,12 +10593,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="E24" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="29"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -10411,7 +10611,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -10428,10 +10628,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -10479,7 +10679,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -10496,7 +10696,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -10693,10 +10893,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -10710,10 +10910,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -10831,10 +11031,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -10849,10 +11049,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -10901,10 +11101,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -10917,9 +11117,9 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="28"/>
@@ -10935,9 +11135,9 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="28"/>
@@ -10987,7 +11187,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>48</v>
@@ -11004,7 +11204,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>50</v>
@@ -11021,10 +11221,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -11040,10 +11240,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -11056,12 +11256,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>212</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -11074,12 +11274,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>207</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -11092,7 +11292,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>143</v>
@@ -11109,10 +11309,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -11160,7 +11360,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>158</v>
@@ -11177,7 +11377,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>159</v>
@@ -11377,10 +11577,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -11394,10 +11594,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -11515,10 +11715,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -11533,10 +11733,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="26"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
@@ -11566,7 +11766,7 @@
         <v>169</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>49</v>
@@ -11585,10 +11785,10 @@
       <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -11603,10 +11803,10 @@
       <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="26"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
@@ -11619,7 +11819,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
         <v>48</v>
@@ -11670,7 +11870,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>48</v>
@@ -11687,7 +11887,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>50</v>
@@ -11704,10 +11904,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -11723,10 +11923,10 @@
       <c r="D22" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="26"/>
+      <c r="E22" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -11739,12 +11939,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="26"/>
+        <v>209</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
@@ -11757,12 +11957,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="26"/>
+        <v>189</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -11775,7 +11975,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>143</v>
@@ -11792,10 +11992,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -11843,7 +12043,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>158</v>
@@ -11860,7 +12060,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>159</v>
@@ -12059,10 +12259,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -12076,10 +12276,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -12252,7 +12452,7 @@
         <v>169</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>49</v>
@@ -12271,10 +12471,10 @@
       <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -12289,10 +12489,10 @@
       <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" s="26"/>
+      <c r="E15" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
@@ -12305,10 +12505,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
@@ -12356,7 +12556,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>48</v>
@@ -12373,7 +12573,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>50</v>
@@ -12390,10 +12590,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
@@ -12410,10 +12610,10 @@
         <v>106</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
@@ -12427,13 +12627,13 @@
         <v>31</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
@@ -12447,13 +12647,13 @@
         <v>167</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
@@ -12467,7 +12667,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>143</v>
@@ -12484,10 +12684,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -12535,7 +12735,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>158</v>
@@ -12552,7 +12752,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>159</v>
@@ -12746,10 +12946,10 @@
         <v>7</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" t="s">
         <v>215</v>
-      </c>
-      <c r="E2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -12763,10 +12963,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
@@ -12958,10 +13158,10 @@
       <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="26"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -12976,10 +13176,10 @@
       <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" s="26"/>
+      <c r="E15" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
@@ -12992,10 +13192,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
@@ -13043,7 +13243,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>48</v>
@@ -13060,7 +13260,7 @@
         <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>50</v>
@@ -13077,10 +13277,10 @@
         <v>29</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
@@ -13097,10 +13297,10 @@
         <v>106</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
@@ -13117,10 +13317,10 @@
         <v>170</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
@@ -13134,13 +13334,13 @@
         <v>167</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
@@ -13154,7 +13354,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>143</v>
@@ -13171,10 +13371,10 @@
         <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
@@ -13222,7 +13422,7 @@
         <v>144</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>158</v>
@@ -13239,7 +13439,7 @@
         <v>145</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>159</v>

--- a/input_tool/edu_indicator_labelling.xlsx
+++ b/input_tool/edu_indicator_labelling.xlsx
@@ -5,37 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\albertoramirez\Projects\EduAnalysisTool-v2-worktrees\strata-lvl-metadata\input_tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlbertoRAMIREZ\Desktop\EduAnalysisTool DEMO\EduAnalysisTool-main\input_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865E928E-0D7A-4E5C-849C-67014FEBC9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D75660-3424-4F84-837E-C7432173871E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3330" windowWidth="29040" windowHeight="16440" tabRatio="834" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update_survey" sheetId="6" r:id="rId1"/>
     <sheet name="original" sheetId="22" r:id="rId2"/>
-    <sheet name="update_choices" sheetId="7" r:id="rId3"/>
-    <sheet name="OPT" sheetId="23" r:id="rId4"/>
-    <sheet name="BFA" sheetId="21" r:id="rId5"/>
-    <sheet name="LBN" sheetId="20" r:id="rId6"/>
-    <sheet name="HTI" sheetId="19" r:id="rId7"/>
-    <sheet name="ETH" sheetId="18" r:id="rId8"/>
-    <sheet name="DRC" sheetId="17" r:id="rId9"/>
-    <sheet name="SSD" sheetId="16" r:id="rId10"/>
-    <sheet name="SOM" sheetId="15" r:id="rId11"/>
-    <sheet name="MMR" sheetId="14" r:id="rId12"/>
-    <sheet name="MLI" sheetId="13" r:id="rId13"/>
-    <sheet name="KEN" sheetId="12" r:id="rId14"/>
-    <sheet name="MOZ" sheetId="11" r:id="rId15"/>
-    <sheet name="CAR" sheetId="8" r:id="rId16"/>
-    <sheet name="AFG" sheetId="9" r:id="rId17"/>
-    <sheet name="SDN" sheetId="10" r:id="rId18"/>
+    <sheet name="00L" sheetId="24" r:id="rId3"/>
+    <sheet name="update_choices" sheetId="7" r:id="rId4"/>
+    <sheet name="OPT" sheetId="23" r:id="rId5"/>
+    <sheet name="BFA" sheetId="21" r:id="rId6"/>
+    <sheet name="LBN" sheetId="20" r:id="rId7"/>
+    <sheet name="HTI" sheetId="19" r:id="rId8"/>
+    <sheet name="ETH" sheetId="18" r:id="rId9"/>
+    <sheet name="DRC" sheetId="17" r:id="rId10"/>
+    <sheet name="SSD" sheetId="16" r:id="rId11"/>
+    <sheet name="SOM" sheetId="15" r:id="rId12"/>
+    <sheet name="MMR" sheetId="14" r:id="rId13"/>
+    <sheet name="MLI" sheetId="13" r:id="rId14"/>
+    <sheet name="KEN" sheetId="12" r:id="rId15"/>
+    <sheet name="MOZ" sheetId="11" r:id="rId16"/>
+    <sheet name="CAR" sheetId="8" r:id="rId17"/>
+    <sheet name="AFG" sheetId="9" r:id="rId18"/>
+    <sheet name="SDN" sheetId="10" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">OPT!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">OPT!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">original!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">update_choices!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">update_choices!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">update_survey!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3566" uniqueCount="240">
   <si>
     <t>theme</t>
   </si>
@@ -788,7 +789,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -906,6 +907,36 @@
       <color rgb="FF58585A"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF58585A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1049,7 +1080,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1120,11 +1151,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1153,18 +1179,59 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="20% - Accent6" xfId="6" builtinId="50"/>
@@ -1448,10 +1515,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="26" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="15" t="s">
@@ -1463,13 +1530,13 @@
       <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="31"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="15" t="s">
@@ -1481,13 +1548,13 @@
       <c r="E2" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="31" t="s">
+      <c r="A3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
@@ -1499,13 +1566,13 @@
       <c r="E3" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="F3" s="31"/>
+      <c r="F3" s="26"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="31" t="s">
+      <c r="A4" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -1514,16 +1581,16 @@
       <c r="D4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="31"/>
+      <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="31" t="s">
+      <c r="A5" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -1535,13 +1602,13 @@
       <c r="E5" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="31"/>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31" t="s">
+      <c r="A6" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -1553,13 +1620,13 @@
       <c r="E6" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="31"/>
+      <c r="F6" s="26"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="31" t="s">
+      <c r="A7" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="15" t="s">
@@ -1571,13 +1638,13 @@
       <c r="E7" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="31"/>
+      <c r="F7" s="26"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="31" t="s">
+      <c r="A8" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="15" t="s">
@@ -1589,13 +1656,13 @@
       <c r="E8" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F8" s="31"/>
+      <c r="F8" s="26"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="31" t="s">
+      <c r="A9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="15" t="s">
@@ -1607,13 +1674,13 @@
       <c r="E9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="31"/>
+      <c r="F9" s="26"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="31" t="s">
+      <c r="A10" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="15" t="s">
@@ -1622,16 +1689,16 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="43"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="31" t="s">
+      <c r="A11" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -1640,178 +1707,178 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="44"/>
+      <c r="F11" s="43"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="33"/>
+      <c r="F12" s="28"/>
     </row>
     <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="34" t="s">
+      <c r="A13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="34" t="s">
+      <c r="E13" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="33"/>
+      <c r="F13" s="28"/>
     </row>
     <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="36" t="s">
+      <c r="A14" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="F14" s="47"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="36" t="s">
+      <c r="A15" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="F15" s="48"/>
+      <c r="F15" s="47"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="36" t="s">
+      <c r="A16" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="35"/>
+      <c r="F16" s="30"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="38" t="s">
+      <c r="A17" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="37"/>
+      <c r="F17" s="32"/>
     </row>
     <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="38" t="s">
+      <c r="A18" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="37"/>
+      <c r="F18" s="32"/>
     </row>
     <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="38" t="s">
+      <c r="A19" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="37"/>
+      <c r="F19" s="32"/>
     </row>
     <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="A20" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="33" t="s">
         <v>226</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="37"/>
+      <c r="F20" s="32"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="31" t="s">
+      <c r="A21" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>161</v>
       </c>
       <c r="C21" s="15" t="s">
@@ -1823,67 +1890,67 @@
       <c r="E21" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="F21" s="31"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A22" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="40" t="s">
+      <c r="A22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="51"/>
+      <c r="F22" s="37"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A23" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="40" t="s">
+      <c r="A23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="F23" s="51"/>
+      <c r="F23" s="37"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A24" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="40" t="s">
+      <c r="A24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="E24" s="49" t="s">
+      <c r="E24" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="52"/>
+      <c r="F24" s="39"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A25" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="31" t="s">
+      <c r="A25" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="15" t="s">
@@ -1895,13 +1962,13 @@
       <c r="E25" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F25" s="31"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A26" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="31" t="s">
+      <c r="A26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="26" t="s">
         <v>127</v>
       </c>
       <c r="C26" s="15" t="s">
@@ -1913,13 +1980,13 @@
       <c r="E26" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="F26" s="31"/>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="31" t="s">
+      <c r="A27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="15" t="s">
@@ -1931,13 +1998,13 @@
       <c r="E27" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="31"/>
+      <c r="F27" s="26"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="31" t="s">
+      <c r="A28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="15" t="s">
@@ -1949,13 +2016,13 @@
       <c r="E28" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="F28" s="31"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="31" t="s">
+      <c r="A29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="15" t="s">
@@ -1967,13 +2034,13 @@
       <c r="E29" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="F29" s="31"/>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="31" t="s">
+      <c r="A30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="15" t="s">
@@ -1985,13 +2052,13 @@
       <c r="E30" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="F30" s="31"/>
+      <c r="F30" s="26"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="31" t="s">
+      <c r="A31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="15" t="s">
@@ -2003,13 +2070,13 @@
       <c r="E31" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="F31" s="31"/>
+      <c r="F31" s="26"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="31" t="s">
+      <c r="A32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="15" t="s">
@@ -2021,13 +2088,13 @@
       <c r="E32" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="F32" s="31"/>
+      <c r="F32" s="26"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="31" t="s">
+      <c r="A33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="15" t="s">
@@ -2039,13 +2106,13 @@
       <c r="E33" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="F33" s="31"/>
+      <c r="F33" s="26"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="31" t="s">
+      <c r="A34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="15" t="s">
@@ -2057,13 +2124,13 @@
       <c r="E34" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="F34" s="31"/>
+      <c r="F34" s="26"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="31" t="s">
+      <c r="A35" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="15" t="s">
@@ -2072,13 +2139,13 @@
       <c r="D35" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F35" s="31"/>
+      <c r="F35" s="26"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="31" t="s">
+      <c r="A36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="15" t="s">
@@ -2087,13 +2154,13 @@
       <c r="D36" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="31"/>
+      <c r="F36" s="26"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="31" t="s">
+      <c r="A37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="15" t="s">
@@ -2102,13 +2169,13 @@
       <c r="D37" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="31"/>
+      <c r="F37" s="26"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="31" t="s">
+      <c r="A38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="15" t="s">
@@ -2117,13 +2184,13 @@
       <c r="D38" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="F38" s="31"/>
+      <c r="F38" s="26"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="31" t="s">
+      <c r="A39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="15" t="s">
@@ -2132,7 +2199,7 @@
       <c r="D39" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="F39" s="31"/>
+      <c r="F39" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2150,6 +2217,693 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1430A0F1-2F5D-43E5-9E49-8E679EDD81F4}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="13.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.69921875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="41.69921875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="94.8984375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="52.19921875" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="48"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="48"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C98E618-344A-487D-B00E-EFB2C24E3770}">
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -2326,10 +3080,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -2344,10 +3098,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -2396,10 +3150,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -2414,10 +3168,10 @@
       <c r="D15" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -2432,10 +3186,10 @@
       <c r="D16" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -2535,10 +3289,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -2553,10 +3307,10 @@
       <c r="D23" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -2571,10 +3325,10 @@
       <c r="D24" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -2831,687 +3585,6 @@
       </c>
       <c r="E40" s="15" t="s">
         <v>218</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E22:F22"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA04313-1E16-4C5B-AB02-8927EAB717AE}">
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="2" width="53.5" style="7"/>
-    <col min="3" max="5" width="53.5" style="15"/>
-    <col min="6" max="16384" width="53.5" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="27"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="27"/>
-    </row>
-    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="27"/>
-    </row>
-    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="27"/>
-    </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F23" s="27"/>
-    </row>
-    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F24" s="27"/>
-    </row>
-    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3530,7 +3603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBB2A30-1E77-42F1-964E-A72E9BDDBED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA04313-1E16-4C5B-AB02-8927EAB717AE}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3705,10 +3778,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -3723,10 +3796,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -3756,7 +3829,7 @@
         <v>169</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>49</v>
@@ -3775,10 +3848,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -3793,10 +3866,10 @@
       <c r="D15" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -3811,10 +3884,10 @@
       <c r="D16" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -3914,10 +3987,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -3930,12 +4003,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="E23" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="E23" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -3950,10 +4023,10 @@
       <c r="D24" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -4211,7 +4284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FDAFB7B-CACC-4A95-AEE0-FBF416C1C9E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBB2A30-1E77-42F1-964E-A72E9BDDBED9}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
@@ -4386,10 +4459,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -4404,10 +4477,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -4456,10 +4529,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="F14" s="27"/>
+      <c r="E14" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -4472,12 +4545,12 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="F15" s="28"/>
+        <v>229</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -4490,12 +4563,12 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="F16" s="28"/>
+        <v>224</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -4595,10 +4668,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="F22" s="27"/>
+      <c r="E22" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -4611,12 +4684,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="F23" s="27"/>
+        <v>206</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -4629,12 +4702,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="F24" s="27"/>
+        <v>207</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -4892,7 +4965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C9AFB8-F0F3-4AAA-AA27-0292EA78AA26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FDAFB7B-CACC-4A95-AEE0-FBF416C1C9E5}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5067,10 +5140,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -5085,10 +5158,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -5137,10 +5210,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="27"/>
+      <c r="E14" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -5155,10 +5228,10 @@
       <c r="D15" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="E15" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="28"/>
+      <c r="E15" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -5173,10 +5246,10 @@
       <c r="D16" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="E16" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="28"/>
+      <c r="E16" s="52" t="s">
+        <v>232</v>
+      </c>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -5276,10 +5349,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="27"/>
+      <c r="E22" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -5294,10 +5367,10 @@
       <c r="D23" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="E23" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F23" s="27"/>
+      <c r="E23" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -5312,10 +5385,10 @@
       <c r="D24" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F24" s="27"/>
+      <c r="E24" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -5573,7 +5646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3426F2-D478-46D5-B931-E2053F6BF542}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C9AFB8-F0F3-4AAA-AA27-0292EA78AA26}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5748,10 +5821,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -5766,10 +5839,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -5818,10 +5891,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -5834,12 +5907,12 @@
         <v>27</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="E15" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -5852,12 +5925,12 @@
         <v>28</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="E16" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="E16" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -5957,10 +6030,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -5973,12 +6046,12 @@
         <v>31</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -5991,12 +6064,12 @@
         <v>167</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="E24" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -6254,6 +6327,687 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3426F2-D478-46D5-B931-E2053F6BF542}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="53.5" style="7"/>
+    <col min="3" max="5" width="53.5" style="15"/>
+    <col min="6" max="16384" width="53.5" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="48"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="48"/>
+    </row>
+    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="48"/>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="50"/>
+    </row>
+    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="50"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A17" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A19" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="48"/>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="48"/>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="48"/>
+    </row>
+    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E22:F22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93BDC91-E487-4F88-AEAB-B2FA5E4CA8B4}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -6432,10 +7186,10 @@
       <c r="D10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -6450,10 +7204,10 @@
       <c r="D11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
@@ -6502,10 +7256,10 @@
       <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -6520,10 +7274,10 @@
       <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="F15" s="27"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
@@ -6640,10 +7394,10 @@
       <c r="D22" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -6658,10 +7412,10 @@
       <c r="D23" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
@@ -6676,10 +7430,10 @@
       <c r="D24" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -6920,720 +7674,6 @@
       <c r="D39" s="7" t="s">
         <v>175</v>
       </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04631CBF-6FD9-45D1-9C42-22D5C9F097A4}">
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="13.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.69921875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="41.69921875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="94.8984375" style="15" customWidth="1"/>
-    <col min="5" max="5" width="52.19921875" style="15" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="31"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="F2" s="31"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="F3" s="31"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="31"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" s="31"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="31"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="31"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="31"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="31"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="43"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="44"/>
-    </row>
-    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A12" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="33"/>
-    </row>
-    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A13" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="33"/>
-    </row>
-    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A14" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>181</v>
-      </c>
-      <c r="F14" s="47"/>
-    </row>
-    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A15" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="F15" s="48"/>
-    </row>
-    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A16" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="35"/>
-    </row>
-    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A17" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="37"/>
-    </row>
-    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A18" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="37"/>
-    </row>
-    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A19" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="37"/>
-    </row>
-    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A20" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="37"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="F21" s="31"/>
-    </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A22" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" s="51"/>
-    </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A23" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>239</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>184</v>
-      </c>
-      <c r="F23" s="51"/>
-    </row>
-    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A24" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="F24" s="52"/>
-    </row>
-    <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A25" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="31"/>
-    </row>
-    <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
-      <c r="A26" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="F26" s="31"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="31"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" s="31"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="F29" s="31"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F30" s="31"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" s="31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="F32" s="31"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F33" s="31"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="F34" s="31"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="F35" s="31"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="F36" s="31"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" s="31"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="F38" s="31"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="F39" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7650,6 +7690,720 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04631CBF-6FD9-45D1-9C42-22D5C9F097A4}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="13.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.69921875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="41.69921875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="94.8984375" style="15" customWidth="1"/>
+    <col min="5" max="5" width="52.19921875" style="15" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2" s="26"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" s="26"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="26"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="26"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="26"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="26"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="26"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="26"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="41"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="43"/>
+    </row>
+    <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A12" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="45"/>
+    </row>
+    <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="47"/>
+    </row>
+    <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A16" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="30"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A17" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="32"/>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="32"/>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="32"/>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A20" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="32"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="F21" s="26"/>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" s="37"/>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="37"/>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="F24" s="39"/>
+    </row>
+    <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
+      <c r="A25" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" s="26"/>
+    </row>
+    <row r="26" spans="1:6" ht="36" x14ac:dyDescent="0.4">
+      <c r="A26" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F26" s="26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="26"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="26"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="26"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" s="26"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="26"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" s="26"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F33" s="26"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F34" s="26"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" s="26"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" s="26"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="26"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="F38" s="26"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="F39" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E3B9F7-D347-4317-AB67-0217058F4008}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -7828,10 +8582,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -7846,10 +8600,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -7898,10 +8652,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="28"/>
+      <c r="F14" s="50"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -7916,10 +8670,10 @@
       <c r="D15" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -7934,10 +8688,10 @@
       <c r="D16" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -8515,10 +9269,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -8533,10 +9287,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -8585,10 +9339,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -8603,10 +9357,10 @@
       <c r="D15" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -8621,10 +9375,10 @@
       <c r="D16" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -8724,10 +9478,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -8742,10 +9496,10 @@
       <c r="D23" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -8760,10 +9514,10 @@
       <c r="D24" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -9022,6 +9776,719 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54ACA9B2-F8A8-4D42-8D21-24A3E92B6828}">
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="13.69921875" style="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.69921875" style="54" customWidth="1"/>
+    <col min="3" max="3" width="41.69921875" style="15" customWidth="1"/>
+    <col min="4" max="4" width="94.8984375" style="15" customWidth="1"/>
+    <col min="5" max="5" width="52.19921875" style="15" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="54"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2" s="53"/>
+    </row>
+    <row r="3" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" s="53"/>
+    </row>
+    <row r="4" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="53"/>
+    </row>
+    <row r="5" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="53"/>
+    </row>
+    <row r="6" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="53"/>
+    </row>
+    <row r="7" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="53"/>
+    </row>
+    <row r="8" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="53"/>
+    </row>
+    <row r="9" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="53"/>
+    </row>
+    <row r="10" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="56"/>
+    </row>
+    <row r="11" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="58"/>
+    </row>
+    <row r="12" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="60" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="62"/>
+    </row>
+    <row r="15" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="64"/>
+    </row>
+    <row r="16" spans="1:6" s="63" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="64"/>
+    </row>
+    <row r="17" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="66" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="62"/>
+    </row>
+    <row r="23" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="E23" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="62"/>
+    </row>
+    <row r="24" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="62"/>
+    </row>
+    <row r="25" spans="1:6" s="54" customFormat="1" ht="36" x14ac:dyDescent="0.4">
+      <c r="A25" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" s="53"/>
+    </row>
+    <row r="26" spans="1:6" s="54" customFormat="1" ht="36" x14ac:dyDescent="0.4">
+      <c r="A26" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F26" s="53"/>
+    </row>
+    <row r="27" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="53"/>
+    </row>
+    <row r="28" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="53"/>
+    </row>
+    <row r="29" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="53"/>
+    </row>
+    <row r="30" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" s="53"/>
+    </row>
+    <row r="31" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="53"/>
+    </row>
+    <row r="32" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" s="53"/>
+    </row>
+    <row r="33" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F33" s="53"/>
+    </row>
+    <row r="34" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F34" s="53"/>
+    </row>
+    <row r="35" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" s="15"/>
+      <c r="F35" s="53"/>
+    </row>
+    <row r="36" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="53"/>
+    </row>
+    <row r="37" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="53"/>
+    </row>
+    <row r="38" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="53"/>
+    </row>
+    <row r="39" spans="1:6" s="54" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
@@ -9487,7 +10954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37EE543-B5CB-4185-B91B-2A9A8CC3DA4C}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -9666,10 +11133,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -9684,10 +11151,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -9736,10 +11203,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -9754,10 +11221,10 @@
       <c r="D15" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -9772,10 +11239,10 @@
       <c r="D16" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -9875,10 +11342,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -9893,10 +11360,10 @@
       <c r="D23" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -9911,10 +11378,10 @@
       <c r="D24" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -10172,7 +11639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78ED0E70-DB3B-451B-8866-F48A2CB32CE9}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -10351,10 +11818,10 @@
       <c r="D10" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -10369,10 +11836,10 @@
       <c r="D11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -10421,10 +11888,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="F14" s="28"/>
+      <c r="F14" s="50"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -10439,10 +11906,10 @@
       <c r="D15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -10559,10 +12026,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="F22" s="26"/>
+      <c r="F22" s="51"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
@@ -10577,10 +12044,10 @@
       <c r="D23" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="F23" s="26"/>
+      <c r="F23" s="51"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
@@ -10595,10 +12062,10 @@
       <c r="D24" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="26"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -10854,7 +12321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B023821-20D2-4192-846D-05966B68C2F4}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="53.5" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -11031,10 +12498,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -11049,10 +12516,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" s="11" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
@@ -11101,10 +12568,10 @@
       <c r="D14" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
@@ -11119,10 +12586,10 @@
       <c r="D15" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="28"/>
+      <c r="F15" s="50"/>
     </row>
     <row r="16" spans="1:6" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
@@ -11137,10 +12604,10 @@
       <c r="D16" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="50"/>
     </row>
     <row r="17" spans="1:6" s="12" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
@@ -11240,10 +12707,10 @@
       <c r="D22" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
@@ -11258,10 +12725,10 @@
       <c r="D23" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -11276,10 +12743,10 @@
       <c r="D24" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -11536,7 +13003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E598F01-CD75-4BC5-AD14-CB9738585B67}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -11715,10 +13182,10 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="27"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -11733,10 +13200,10 @@
       <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="27"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
@@ -11785,10 +13252,10 @@
       <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -11803,10 +13270,10 @@
       <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="27"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
@@ -11923,10 +13390,10 @@
       <c r="D22" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F22" s="27"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
@@ -11941,10 +13408,10 @@
       <c r="D23" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="27"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
@@ -11959,10 +13426,10 @@
       <c r="D24" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="27"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
       <c r="A25" s="7" t="s">
@@ -12218,7 +13685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664A1F51-322B-4DAC-988D-ED5F1BCA03D1}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
@@ -12471,10 +13938,10 @@
       <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -12489,10 +13956,10 @@
       <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="F15" s="27"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
@@ -12648,693 +14115,6 @@
       </c>
       <c r="D24" s="24" t="s">
         <v>189</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="38.4" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1430A0F1-2F5D-43E5-9E49-8E679EDD81F4}">
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="13.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.69921875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="41.69921875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="94.8984375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="52.19921875" style="7" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="E3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="27"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="F15" s="27"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>194</v>
